--- a/data/trans_camb/IP1020-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-1.565542408467311</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.084930126097297</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.04684714616562981</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.135420666074322</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.8410839794684812</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2.644824012327438</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-3.502724305012509</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.1658119630720771</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.275965731254127</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-0.5728154196716632</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-2.187234734531581</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.4094460095589404</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>-0.1562674187258732</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.677533776038305</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.794795726428887</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.460209646949997</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.27195738529237</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>6.070856609499593</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.7737231365067677</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1.52463567908391</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.02515933219043392</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1.146830966269154</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.4325128348867152</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.360054833134608</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.2972296364616905</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.7333504588107826</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.4591210423083255</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.7765988991442165</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.06283200980952963</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.7970585817888884</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>6.655703651444932</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>2.160876243888255</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>6.162808140166121</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.3012952761511061</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>4.571473463189729</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>3.061689314799955</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.759905009421011</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.190246114514319</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.6790305156846147</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.9385090446627694</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.096376954991534</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>1.124386840168043</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.5367026316309819</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.359289506852945</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.962851312913828</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.5352150874913472</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.5199522268750255</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>5.890811220150396</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.590796554276654</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.7139822763095097</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.269560204045701</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.723205264215371</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2.933495360018061</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>3.824866625102503</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>3.447857530141774</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.5314379334042787</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.3031831564693859</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.6169202103373604</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.7206932160418885</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>0.2356972101983868</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.1258855229518656</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.9832156020187809</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3066325447226516</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2813367872970971</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -824,13 +892,18 @@
       </c>
       <c r="C15" s="6" t="inlineStr"/>
       <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="n">
+        <v>1.029785168649729</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2.586358844031228</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>3.036298074453617</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>3.256665838991253</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +916,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-0.3572233942404857</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.2438148424809883</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.332340475121505</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.430021543319624</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.8434914690284554</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.9376863494450549</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +942,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-2.880190564770162</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.941025345045232</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4.241927103490744</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.244341644466371</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-2.71839216117271</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-1.220857953123225</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +968,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>3.220422063829847</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.181974926331848</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.149180753097089</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6.316551350824227</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.9665140634578607</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>3.304374927025488</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +994,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.1541001236705178</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.1051775947062818</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.4589574219011354</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.8370806438080202</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.3237762848503468</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.3599332224757355</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1020,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.848897451759403</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.8062257093391975</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.9074672558748947</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.3916986190738528</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.7665361068009197</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.3706808424335225</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1046,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>4.994716067146829</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>2.85647092312403</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1.287542068301823</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>3.798815155586787</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.668707174597305</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2.139262681738661</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1076,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>0.7285626829034625</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4.063860256970407</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-5.685559337313953</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-2.165233595732702</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-2.154919694273474</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>1.232695645503283</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1102,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1.985753081419267</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-12.24752772808937</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-8.687924084360645</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-4.750259055140773</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-1.465204098860942</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1128,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>3.654640332792491</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>7.981258610142179</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-2.55970050305767</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.075324816448988</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.3703121818704508</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>4.068927896514807</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1154,28 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.3808303576259271</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.8405253732155893</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.4808123338662052</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1020,12 +1187,15 @@
       <c r="C26" s="6" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
       <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="n">
+        <v>-0.8572825302451484</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.4299617837952245</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1037,12 +1207,15 @@
       <c r="C27" s="6" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="n">
+        <v>1.032125660825271</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>2.204642894793664</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>4.065467236253517</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1228,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>0.2718219204166598</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1.939027759967439</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-1.318431509036831</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.8974107538171679</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.5029408116659682</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1.427614224841523</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1254,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-0.7441054992560691</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0.5772135599993564</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-2.567304333667347</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-0.6546908158690173</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-1.312802362712361</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0.3187479777557242</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1280,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>1.384488767166014</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3.401901986146492</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>-0.2124761779213672</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>2.776578714934986</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.2689152732934638</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>2.520177129197719</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1306,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.1876677131413206</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>1.338718028600625</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.497036112409998</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.3383153006090288</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.2470230969081152</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.7011832780924703</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1332,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.410541874862385</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.2410368621226614</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.7451650303621805</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.2327555827071326</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.5243334831196547</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0.1224037735340991</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1358,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>1.456897227420692</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>3.517518860630478</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>-0.01396640169376858</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1.297046306832459</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.1964158845969483</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>1.488986434948121</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1386,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
